--- a/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
@@ -10,7 +10,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ticket Medio" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ticket Medio'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -491,9 +493,9 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -513,6 +515,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -534,10 +537,19 @@
         </is>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -546,7 +558,16 @@
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -554,7 +575,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -580,6 +601,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -765,6 +787,15 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
@@ -19,10 +19,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -63,8 +64,26 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -81,6 +100,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="002D2D2D"/>
         <bgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
       </patternFill>
     </fill>
   </fills>
@@ -110,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -129,10 +153,66 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -495,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="1" max="1"/>
@@ -539,7 +619,7 @@
     </row>
     <row r="7"/>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Celdas verdes = campos editables</t>
         </is>
@@ -547,13 +627,35 @@
     </row>
     <row r="9"/>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
+      <c r="A10" s="11" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA. En el cash flow también se escriben sin IVA: su capa de IVA (modelo 303) lo añade aparte, porque la tesorería es caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Para editar la estructura o una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/guia-restaurante-gastronomico · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
@@ -577,10 +679,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -601,26 +703,32 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
+    <row r="3">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA. En el cash flow también se escriben sin IVA: su capa de IVA (modelo 303) lo añade aparte, porque la tesorería es caja.</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
           <t>Concepto</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Escenario 1</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Escenario 2</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Escenario 3</t>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>Pesimista</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>Realista</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Optimista</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
@@ -635,9 +743,15 @@
           <t>% comensales menú degustación largo</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
+      <c r="B5" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="C5" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D5" s="14" t="n">
+        <v>0.65</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -645,9 +759,15 @@
           <t>Precio menú largo (€)</t>
         </is>
       </c>
-      <c r="B6" s="8" t="n"/>
-      <c r="C6" s="8" t="n"/>
-      <c r="D6" s="8" t="n"/>
+      <c r="B6" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="C6" s="15" t="n">
+        <v>130</v>
+      </c>
+      <c r="D6" s="15" t="n">
+        <v>120</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -655,9 +775,15 @@
           <t>% comensales menú degustación corto</t>
         </is>
       </c>
-      <c r="B7" s="8" t="n"/>
-      <c r="C7" s="8" t="n"/>
-      <c r="D7" s="8" t="n"/>
+      <c r="B7" s="14" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C7" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="D7" s="14" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -665,9 +791,15 @@
           <t>Precio menú corto (€)</t>
         </is>
       </c>
-      <c r="B8" s="8" t="n"/>
-      <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
+      <c r="B8" s="15" t="n">
+        <v>70</v>
+      </c>
+      <c r="C8" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>72</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -675,9 +807,15 @@
           <t>% comensales carta</t>
         </is>
       </c>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
+      <c r="B9" s="14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>0.15</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -685,9 +823,15 @@
           <t>Ticket medio carta (€)</t>
         </is>
       </c>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="B10" s="15" t="n">
+        <v>75</v>
+      </c>
+      <c r="C10" s="15" t="n">
+        <v>85</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>82</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -695,9 +839,15 @@
           <t>% comensales con maridaje vinos</t>
         </is>
       </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
+      <c r="B11" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -705,9 +855,15 @@
           <t>Precio maridaje (€)</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="B12" s="15" t="n">
+        <v>55</v>
+      </c>
+      <c r="C12" s="15" t="n">
+        <v>60</v>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>57</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -715,9 +871,15 @@
           <t>% comensales con copa de vino</t>
         </is>
       </c>
-      <c r="B13" s="8" t="n"/>
-      <c r="C13" s="8" t="n"/>
-      <c r="D13" s="8" t="n"/>
+      <c r="B13" s="14" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" s="14" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>0.2</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -725,12 +887,39 @@
           <t>Precio copa media (€)</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
+      <c r="B14" s="15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C14" s="15" t="n">
+        <v>14</v>
+      </c>
+      <c r="D14" s="15" t="n">
+        <v>14</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="inlineStr"/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>% de comensales asignado (debe sumar 100 %)</t>
+        </is>
+      </c>
+      <c r="B15" s="16">
+        <f>B5+B7+B9</f>
+        <v>1.0</v>
+      </c>
+      <c r="C15" s="16">
+        <f>C5+C7+C9</f>
+        <v>1.0</v>
+      </c>
+      <c r="D15" s="16">
+        <f>D5+D7+D9</f>
+        <v>1.0</v>
+      </c>
+      <c r="E15" s="17" t="inlineStr">
+        <is>
+          <t>Los tramos del menú se reparten el 100 % de los comensales. El maridaje y la copa NO entran aquí: son consumo adicional sobre el mismo comensal, por eso pueden sumar más de 100 %.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
@@ -738,9 +927,18 @@
           <t>TICKET MEDIO PONDERADO (€)</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="B16" s="18">
+        <f>B5*B6+B7*B8+B9*B10+B11*B12+B13*B14</f>
+        <v>99.8</v>
+      </c>
+      <c r="C16" s="18">
+        <f>C5*C6+C7*C8+C9*C10+C11*C12+C13*C14</f>
+        <v>123.2</v>
+      </c>
+      <c r="D16" s="18">
+        <f>D5*D6+D7*D8+D9*D10+D11*D12+D13*D14</f>
+        <v>136.0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -748,9 +946,15 @@
           <t>Cubiertos/día</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="8" t="n"/>
-      <c r="D17" s="8" t="n"/>
+      <c r="B17" s="19" t="n">
+        <v>60</v>
+      </c>
+      <c r="C17" s="19" t="n">
+        <v>70</v>
+      </c>
+      <c r="D17" s="19" t="n">
+        <v>78</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
@@ -758,9 +962,18 @@
           <t>Facturación diaria (€)</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="8" t="n"/>
-      <c r="D18" s="8" t="n"/>
+      <c r="B18" s="20">
+        <f>B16*B17</f>
+        <v>5988.0</v>
+      </c>
+      <c r="C18" s="20">
+        <f>C16*C17</f>
+        <v>8624.0</v>
+      </c>
+      <c r="D18" s="20">
+        <f>D16*D17</f>
+        <v>10608.0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="inlineStr">
@@ -768,9 +981,15 @@
           <t>Días abierto/mes</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
+      <c r="B19" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="C19" s="19" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" s="19" t="n">
+        <v>22</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
@@ -778,15 +997,135 @@
           <t>Facturación mensual (€)</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="B20" s="20">
+        <f>B18*B19</f>
+        <v>131736.0</v>
+      </c>
+      <c r="C20" s="20">
+        <f>C18*C19</f>
+        <v>189728.0</v>
+      </c>
+      <c r="D20" s="20">
+        <f>D18*D19</f>
+        <v>233376.0</v>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="21" t="inlineStr">
+        <is>
+          <t>IVA Y CUADRE CON EL P&amp;L DE ESCENARIOS</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="n"/>
+      <c r="C22" s="22" t="n"/>
+      <c r="D22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Tipo de IVA de los precios de esta hoja (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="24" t="inlineStr">
+        <is>
+          <t>Los precios de arriba se escriben SIN IVA, igual que el P&amp;L. Esta celda solo sirve para la fila «Ticket medio CON IVA», que es el precio que el comensal ve en la carta: 10 % general de restauración y 21 % en la parte de bebida alcohólica.</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ticket medio CON IVA — el precio que ve el comensal (€)</t>
+        </is>
+      </c>
+      <c r="B24" s="22">
+        <f>IF(B16="","",B16*(1+$B$23))</f>
+        <v>109.78</v>
+      </c>
+      <c r="C24" s="22">
+        <f>IF(C16="","",C16*(1+$B$23))</f>
+        <v>135.52</v>
+      </c>
+      <c r="D24" s="22">
+        <f>IF(D16="","",D16*(1+$B$23))</f>
+        <v>149.60000000000002</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Facturación mensual del P&amp;L de escenarios (€) — la que va al banco</t>
+        </is>
+      </c>
+      <c r="B25" s="22" t="n">
+        <v>131736</v>
+      </c>
+      <c r="C25" s="22" t="n">
+        <v>189728</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>233376</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Diferencia con este simulador (%)</t>
+        </is>
+      </c>
+      <c r="B26" s="16">
+        <f>IF(OR(B25="",B25=0,B20=""),"",(B20-B25)/B25)</f>
+        <v>0.0</v>
+      </c>
+      <c r="C26" s="16">
+        <f>IF(OR(C25="",C25=0,C20=""),"",(C20-C25)/C25)</f>
+        <v>0.0</v>
+      </c>
+      <c r="D26" s="16">
+        <f>IF(OR(D25="",D25=0,D20=""),"",(D20-D25)/D25)</f>
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Las dos hojas describen el MISMO restaurante: mismos cubiertos/día y mismos días abiertos. Los tickets de comida y cena del P&amp;L están calibrados contra el ticket ponderado de esta hoja, así que esta fila tiene que dar 0,0 %. Si no lo da, has cambiado un precio aquí y no allí — y la cifra que vale es la del P&amp;L (§7-bis.7).</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <mergeCells count="2">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
   </mergeCells>
+  <conditionalFormatting sqref="B15:D15">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(B15),B15&lt;&gt;1)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B26:D26">
+    <cfRule type="expression" priority="2" dxfId="0" stopIfTrue="1">
+      <formula>=AND(ISNUMBER(B26),B26&gt;0.02)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation sqref="B6 B8 B10 B12 B14 B17 B19 C6 C8 C10 C12 C14 C17 C19 D6 D8 D10 D12 D14 D17 D19" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation sqref="B5 B7 B9 B11 B13 B23 C5 C7 C9 C11 C13 D5 D7 D9 D11 D13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Porcentaje" error="Escribe un porcentaje entre 0 y 1 (0,20 = 20 %)." promptTitle="Porcentaje" prompt="Se escribe en tanto por uno: 0,20 = 20 %." type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1.0</formula2>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>

--- a/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
+++ b/astro-site/public/dl/guia-restaurante-gastronomico/calculadora-ticket-medio.xlsx
@@ -1032,7 +1032,7 @@
       </c>
       <c r="C23" s="24" t="inlineStr">
         <is>
-          <t>Los precios de arriba se escriben SIN IVA, igual que el P&amp;L. Esta celda solo sirve para la fila «Ticket medio CON IVA», que es el precio que el comensal ve en la carta: 10 % general de restauración y 21 % en la parte de bebida alcohólica.</t>
+          <t>Los precios de arriba se escriben SIN IVA, igual que el P&amp;L. Esta celda solo sirve para la fila «Ticket medio CON IVA», que es el precio que el comensal ve en la carta: el 10 % de restauración se aplica a TODO el consumo en sala, comida y bebida alcohólica incluidas (art. 91.Uno.2.2 de la Ley del IVA). El 21 % es el tipo general y solo aplica a la venta para llevar.</t>
         </is>
       </c>
       <c r="D23" s="16" t="n"/>
